--- a/entre_mundos_app/data/projeto.xlsx
+++ b/entre_mundos_app/data/projeto.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -475,7 +475,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Expedição Rio 1° Ed</t>
+          <t>Expedição RJ - Ed 1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
